--- a/Genostar/Pre_genostar/CYPStodo.xlsx
+++ b/Genostar/Pre_genostar/CYPStodo.xlsx
@@ -4,12 +4,14 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11160" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25755" windowHeight="8520" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="CYPS" sheetId="3" r:id="rId2"/>
-    <sheet name="con_ventana" sheetId="4" r:id="rId3"/>
+    <sheet name="Human (hg19)" sheetId="3" r:id="rId1"/>
+    <sheet name="hg19 ventana 5000 (SNPs)" sheetId="4" r:id="rId2"/>
+    <sheet name="Human (hg38)" sheetId="5" r:id="rId3"/>
+    <sheet name="hg38 ventana 5000 (SNVs)" sheetId="6" r:id="rId4"/>
+    <sheet name="hg38 ventana 100.000 (epi)" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -21,28 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
-  <si>
-    <t>cypNAME</t>
-  </si>
-  <si>
-    <t>ensgid</t>
-  </si>
-  <si>
-    <t>chr</t>
-  </si>
-  <si>
-    <t>start</t>
-  </si>
-  <si>
-    <t>END</t>
-  </si>
-  <si>
-    <t>42526812</t>
-  </si>
-  <si>
-    <t>ENSEMBL.ORG</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="14">
   <si>
     <t>ENSG00000100197</t>
   </si>
@@ -90,18 +71,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -124,17 +97,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -413,166 +382,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="26.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2">
-        <v>22</v>
-      </c>
-      <c r="D2">
-        <v>42522501</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3">
-        <v>15</v>
-      </c>
-      <c r="D3">
-        <v>75041186</v>
-      </c>
-      <c r="E3">
-        <v>75048948</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4">
-        <v>19</v>
-      </c>
-      <c r="D4">
-        <v>41497187</v>
-      </c>
-      <c r="E4">
-        <v>41524303</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5">
-        <v>10</v>
-      </c>
-      <c r="D5">
-        <v>96698415</v>
-      </c>
-      <c r="E5">
-        <v>96749848</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>96522438</v>
-      </c>
-      <c r="E6">
-        <v>96615304</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>99354590</v>
-      </c>
-      <c r="E7">
-        <v>99381807</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-      <c r="D8">
-        <v>99245817</v>
-      </c>
-      <c r="E8">
-        <v>99277619</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C11" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>22</v>
       </c>
@@ -583,10 +396,13 @@
         <v>42526812</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>15</v>
       </c>
@@ -597,10 +413,13 @@
         <v>75048948</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>19</v>
       </c>
@@ -611,10 +430,13 @@
         <v>41524303</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>10</v>
       </c>
@@ -625,10 +447,13 @@
         <v>96749848</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>10</v>
       </c>
@@ -639,10 +464,13 @@
         <v>96615304</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>7</v>
       </c>
@@ -653,10 +481,13 @@
         <v>99381807</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -667,7 +498,10 @@
         <v>99277619</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -689,7 +523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -705,7 +539,7 @@
         <v>42531812</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -719,7 +553,7 @@
         <v>75053948</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -733,7 +567,7 @@
         <v>41529303</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -747,7 +581,7 @@
         <v>96754848</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -761,7 +595,7 @@
         <v>96620304</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -775,7 +609,7 @@
         <v>99386807</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -789,7 +623,373 @@
         <v>99282619</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>22</v>
+      </c>
+      <c r="B1">
+        <v>42126499</v>
+      </c>
+      <c r="C1">
+        <v>42130810</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>15</v>
+      </c>
+      <c r="B2">
+        <v>74748845</v>
+      </c>
+      <c r="C2">
+        <v>74756607</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>19</v>
+      </c>
+      <c r="B3">
+        <v>40991282</v>
+      </c>
+      <c r="C3">
+        <v>41018398</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>94938658</v>
+      </c>
+      <c r="C4">
+        <v>94990091</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>94762681</v>
+      </c>
+      <c r="C5">
+        <v>94855547</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>99756967</v>
+      </c>
+      <c r="C6">
+        <v>99784184</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>99648194</v>
+      </c>
+      <c r="C7">
+        <v>99679996</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>22</v>
+      </c>
+      <c r="B1">
+        <v>42121499</v>
+      </c>
+      <c r="C1">
+        <v>42135810</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>15</v>
+      </c>
+      <c r="B2">
+        <v>74743845</v>
+      </c>
+      <c r="C2">
+        <v>74761607</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>19</v>
+      </c>
+      <c r="B3">
+        <v>40986282</v>
+      </c>
+      <c r="C3">
+        <v>41023398</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>94933658</v>
+      </c>
+      <c r="C4">
+        <v>94995091</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>94757681</v>
+      </c>
+      <c r="C5">
+        <v>94860547</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>99751967</v>
+      </c>
+      <c r="C6">
+        <v>99789184</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>99643194</v>
+      </c>
+      <c r="C7">
+        <v>99684996</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>22</v>
+      </c>
+      <c r="B1">
+        <v>42026499</v>
+      </c>
+      <c r="C1">
+        <v>42230810</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>15</v>
+      </c>
+      <c r="B2">
+        <v>74648845</v>
+      </c>
+      <c r="C2">
+        <v>74856607</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>19</v>
+      </c>
+      <c r="B3">
+        <v>40891282</v>
+      </c>
+      <c r="C3">
+        <v>41118398</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>94838658</v>
+      </c>
+      <c r="C4">
+        <v>95090091</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>94662681</v>
+      </c>
+      <c r="C5">
+        <v>94955547</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>99656967</v>
+      </c>
+      <c r="C6">
+        <v>99884184</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>99548194</v>
+      </c>
+      <c r="C7">
+        <v>99779996</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
